--- a/results/Big_Numbers_UF.xlsx
+++ b/results/Big_Numbers_UF.xlsx
@@ -505,10 +505,10 @@
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="n">
-        <v>7426</v>
+        <v>8043</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>843.3</v>
+        <v>913.3</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>1</v>
@@ -519,10 +519,10 @@
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="4" t="n">
-        <v>715</v>
+        <v>748</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>22.2</v>
+        <v>23.2</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>1</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="2" t="n">
-        <v>730</v>
+        <v>705</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>0</v>
@@ -547,10 +547,10 @@
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="4" t="n">
-        <v>2419</v>
+        <v>2579</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>56.5</v>
+        <v>60.2</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>1</v>
@@ -561,13 +561,13 @@
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="2" t="n">
-        <v>8930</v>
+        <v>9680</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>60.1</v>
+        <v>65.2</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>4</v>
@@ -575,10 +575,10 @@
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="4" t="n">
-        <v>1554</v>
+        <v>1627</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>16.8</v>
+        <v>17.6</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>1</v>
@@ -589,10 +589,10 @@
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="2" t="n">
-        <v>5161</v>
+        <v>5395</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>173</v>
+        <v>180.9</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>4</v>
@@ -603,10 +603,10 @@
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="4" t="n">
-        <v>10484</v>
+        <v>11013</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>255.6</v>
+        <v>268.5</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>7</v>
@@ -617,27 +617,27 @@
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="2" t="n">
-        <v>32441</v>
+        <v>34321</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>441.4</v>
+        <v>466.9</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="4" t="n">
-        <v>1446</v>
+        <v>1733</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>20.6</v>
+        <v>24.7</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>0</v>
@@ -645,27 +645,27 @@
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="2" t="n">
-        <v>19745</v>
+        <v>20212</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>514.7</v>
+        <v>526.9</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>7</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="4" t="n">
-        <v>5011</v>
+        <v>5311</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>172.7</v>
+        <v>183</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>4</v>
@@ -673,38 +673,38 @@
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="2" t="n">
-        <v>69388</v>
+        <v>74334</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>325.4</v>
+        <v>348.6</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="4" t="n">
-        <v>8650</v>
+        <v>9343</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>99.8</v>
+        <v>107.8</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="2" t="n">
-        <v>2238</v>
+        <v>2267</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>54</v>
+        <v>54.7</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>1</v>
@@ -715,27 +715,27 @@
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="4" t="n">
-        <v>42678</v>
+        <v>45880</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>360.9</v>
+        <v>388</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="2" t="n">
-        <v>4113</v>
+        <v>4399</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>43.1</v>
+        <v>46.1</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>0</v>
@@ -743,27 +743,27 @@
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="4" t="n">
-        <v>1586</v>
+        <v>1689</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="2" t="n">
-        <v>12889</v>
+        <v>13822</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>74.90000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>6</v>
@@ -771,10 +771,10 @@
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="4" t="n">
-        <v>1539</v>
+        <v>1626</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>44.7</v>
+        <v>47.2</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>2</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="2" t="n">
-        <v>6984</v>
+        <v>7946</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>62.2</v>
+        <v>70.8</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>4</v>
@@ -799,10 +799,10 @@
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="4" t="n">
-        <v>682</v>
+        <v>742</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>39.1</v>
+        <v>42.5</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>1</v>
@@ -813,10 +813,10 @@
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="2" t="n">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>17.3</v>
+        <v>16.6</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>0</v>
@@ -827,10 +827,10 @@
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="4" t="n">
-        <v>7389</v>
+        <v>7848</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>91.7</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>2</v>
@@ -841,24 +841,24 @@
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="2" t="n">
-        <v>364195</v>
+        <v>389860</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>792.2</v>
+        <v>848</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>423</v>
+        <v>457</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>226</v>
+        <v>258</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="4" t="n">
-        <v>488</v>
+        <v>511</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>21.3</v>
+        <v>22.3</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>0</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="2" t="n">
-        <v>1696</v>
+        <v>1703</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>107.5</v>
+        <v>108</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>0</v>
